--- a/skills/zia-mta-basemap/examples/twy-e-asbuilt-ducts/material/Material Requirement - TWY E AGL Installation - Rev P08.xlsx
+++ b/skills/zia-mta-basemap/examples/twy-e-asbuilt-ducts/material/Material Requirement - TWY E AGL Installation - Rev P08.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="56">
   <si>
     <t xml:space="preserve">MATERIAL REQUIREMENT — AGL INSTALLATION</t>
   </si>
@@ -139,7 +139,7 @@
     <t xml:space="preserve">mtr</t>
   </si>
   <si>
-    <t xml:space="preserve">Saw cut route length is approx. 420 m over 19 No. runs. 1500 m covers the full manhole-to-light runs (no joints) plus terminations and tails — confirm against the run-by-run lengths now that 19 No. runs are in scope.</t>
+    <t xml:space="preserve">1 No. 2-core 4 sq.mm cable to each fitting, SBC and TCC alike — 7 No. SBC and 12 No. TCC = 19 No. runs. Saw cut route length is approx. 420 m; 1500 m covers the full manhole-to-light runs (no joints) plus terminations and tails — confirm against the run-by-run lengths.</t>
   </si>
   <si>
     <t xml:space="preserve">Masking tape</t>
@@ -181,13 +181,16 @@
     <t xml:space="preserve">3.  Sealant, mortar and backer rod quantities depend on the saw cut width and depth and on the core diameter. Both are set by the saw cut &amp; side-entry shallow base detail drawing, which had not been issued at Rev P08 (hold point H5). Re-check these three lines when it is issued.</t>
   </si>
   <si>
-    <t xml:space="preserve">4.  Secondary cable is ordered against the full manhole-to-light runs (19 No.), not the saw cut length — the cut measures approx. 420 m across the three locations (approx. 300 m LOC-01, 24 m LOC-02, 95 m LOC-03).</t>
+    <t xml:space="preserve">4.  One 2-core 4 sq.mm secondary cable serves each fitting, SBC and TCC alike — 7 No. SBC and 12 No. TCC. Cable is ordered against the full manhole-to-light runs (19 No.), not the saw cut length — the cut measures approx. 420 m across the three locations (approx. 300 m LOC-01, 24 m LOC-02, 95 m LOC-03).</t>
   </si>
   <si>
     <t xml:space="preserve">5.  Saw cut is an interim arrangement agreed between the AGL team, the civil team and ADA AGL. Permanent duct provision follows under the South Rehabilitation works, and is not covered by this requirement.</t>
   </si>
   <si>
-    <t xml:space="preserve">6.  Remaining Qty is a formula (Required − Available). Edit only the Required and Available columns.</t>
+    <t xml:space="preserve">6.  Testing and commissioning is carried out at circuit level and covers the affected fittings together with the fittings on the same circuits that fall outside these works — the series circuits are proved end to end before handover.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.  Remaining Qty is a formula (Required − Available). Edit only the Required and Available columns.</t>
   </si>
 </sst>
 </file>
@@ -730,7 +733,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -1138,14 +1141,26 @@
       <c r="F29" s="27"/>
       <c r="G29" s="27"/>
     </row>
+    <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A26:G26"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A30:G30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/skills/zia-mta-basemap/examples/twy-e-asbuilt-ducts/material/Material Requirement - TWY E AGL Installation - Rev P08.xlsx
+++ b/skills/zia-mta-basemap/examples/twy-e-asbuilt-ducts/material/Material Requirement - TWY E AGL Installation - Rev P08.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
   <si>
     <t xml:space="preserve">MATERIAL REQUIREMENT — AGL INSTALLATION</t>
   </si>
@@ -148,7 +148,7 @@
     <t xml:space="preserve">Box</t>
   </si>
   <si>
-    <t xml:space="preserve">As advised. No basis in the Rev P08 deck.</t>
+    <t xml:space="preserve">As advised, for general protection. The signboard masking is by matt black vinyl sticker — see the separate line below.</t>
   </si>
   <si>
     <t xml:space="preserve">Shallow base 12 inch</t>
@@ -157,6 +157,15 @@
     <t xml:space="preserve">ADDED — the plan needs 13 No. new bases: 11 No. 8" plus 2 No. 12" (LOC-02 TCCECH-03/008 and LOC-03 TCCECH-03/003). Not in the list as issued.</t>
   </si>
   <si>
+    <t xml:space="preserve">Vinyl sticker, matt black — signboard masking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADDED — masks the direction signboards leading to E4 and E6 under Phase 1, R4; removed in Phase 3 before the functionality check. Quantity depends on the number of sign faces and their area, which the deck does not carry — to be measured on site.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dummy plate (8" / 12")</t>
   </si>
   <si>
@@ -172,7 +181,7 @@
     <t xml:space="preserve">NOTES</t>
   </si>
   <si>
-    <t xml:space="preserve">1.  Rows 1–8 are the quantities as advised. Rows 9 and 10 are added, and the connector quantity is revised, so the list covers what the Rev P08 plan requires. Availability of the added lines is to be filled in (yellow cells).</t>
+    <t xml:space="preserve">1.  Rows 1–8 are the quantities as advised. Rows 9 to 11 are added, and the connector quantity is revised, so the list covers what the Rev P08 plan requires. Availability of the added lines is to be filled in (yellow cells).</t>
   </si>
   <si>
     <t xml:space="preserve">2.  The plan needs 13 No. new side-entry shallow bases in total — 11 No. 8" at LOC-01, 1 No. 12" at LOC-02 (TCCECH-03/008) and 1 No. 12" at LOC-03 (TCCECH-03/003).</t>
@@ -187,10 +196,13 @@
     <t xml:space="preserve">5.  Saw cut is an interim arrangement agreed between the AGL team, the civil team and ADA AGL. Permanent duct provision follows under the South Rehabilitation works, and is not covered by this requirement.</t>
   </si>
   <si>
-    <t xml:space="preserve">6.  Testing and commissioning is carried out at circuit level and covers the affected fittings together with the fittings on the same circuits that fall outside these works — the series circuits are proved end to end before handover.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.  Remaining Qty is a formula (Required − Available). Edit only the Required and Available columns.</t>
+    <t xml:space="preserve">6.  The direction signboards leading to E4 and E6 are masked with matt black vinyl sticker under Phase 1 (R4) and unmasked in Phase 3 before the functionality check. The vinyl quantity depends on the number of sign faces and their area — measure on site before ordering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.  Testing and commissioning is carried out at circuit level and covers the affected fittings together with the fittings on the same circuits that fall outside these works — the series circuits are proved end to end before handover.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.  Remaining Qty is a formula (Required − Available). Edit only the Required and Available columns.</t>
   </si>
 </sst>
 </file>
@@ -733,7 +745,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -1040,55 +1052,64 @@
         <v>44</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="19" t="n">
-        <v>16</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D20" s="19"/>
       <c r="E20" s="20"/>
       <c r="F20" s="21" t="str">
         <f aca="false">IF(E20="","",D20-E20)</f>
         <v/>
       </c>
       <c r="G20" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="25" t="n">
-        <f aca="false">COUNTIF(F11:F20,"&gt;0")</f>
+      <c r="A21" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="E21" s="20"/>
+      <c r="F21" s="21" t="str">
+        <f aca="false">IF(E21="","",D21-E21)</f>
+        <v/>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="23"/>
+      <c r="B22" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="25" t="n">
+        <f aca="false">COUNTIF(F11:F21,"&gt;0")</f>
         <v>3</v>
       </c>
-      <c r="G21" s="16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
+      <c r="G22" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="26" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B25" s="27"/>
       <c r="C25" s="27"/>
@@ -1099,7 +1120,7 @@
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="27"/>
@@ -1110,7 +1131,7 @@
     </row>
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B27" s="27"/>
       <c r="C27" s="27"/>
@@ -1121,7 +1142,7 @@
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="27" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B28" s="27"/>
       <c r="C28" s="27"/>
@@ -1132,7 +1153,7 @@
     </row>
     <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B29" s="27"/>
       <c r="C29" s="27"/>
@@ -1143,7 +1164,7 @@
     </row>
     <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B30" s="27"/>
       <c r="C30" s="27"/>
@@ -1152,15 +1173,38 @@
       <c r="F30" s="27"/>
       <c r="G30" s="27"/>
     </row>
+    <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+    </row>
+    <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A24:G24"/>
+  <mergeCells count="8">
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A26:G26"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A32:G32"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/skills/zia-mta-basemap/examples/twy-e-asbuilt-ducts/material/Material Requirement - TWY E AGL Installation - Rev P08.xlsx
+++ b/skills/zia-mta-basemap/examples/twy-e-asbuilt-ducts/material/Material Requirement - TWY E AGL Installation - Rev P08.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Material Requirement" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">'Material Requirement'!$10:$10</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">'Material Requirement'!$11:$11</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="81">
   <si>
     <t xml:space="preserve">MATERIAL REQUIREMENT — AGL INSTALLATION</t>
   </si>
@@ -43,6 +43,12 @@
     <t xml:space="preserve">Rev P08 final scope of work issued 30.07.2026 — 19 No. affected fittings; 13 No. new side-entry shallow bases; approx. 420 m of saw cut</t>
   </si>
   <si>
+    <t xml:space="preserve">Sourcing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two lines fall short of ADB SAFEGATE stock. The project team confirms no ready stock; both are held in ADA inventory and are to be drawn from there.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prepared by</t>
   </si>
   <si>
@@ -67,6 +73,9 @@
     <t xml:space="preserve">Material</t>
   </si>
   <si>
+    <t xml:space="preserve">ADA item code</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unit</t>
   </si>
   <si>
@@ -76,7 +85,13 @@
     <t xml:space="preserve">Available with ADB SAFEGATE</t>
   </si>
   <si>
-    <t xml:space="preserve">Remaining Qty to procure</t>
+    <t xml:space="preserve">Qty requested from ADA inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADA inventory — current stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADA inventory — balance after withdrawal</t>
   </si>
   <si>
     <t xml:space="preserve">Basis / check against the Rev P08 plan</t>
@@ -109,10 +124,13 @@
     <t xml:space="preserve">Shallow base 8 inch</t>
   </si>
   <si>
+    <t xml:space="preserve">10016966</t>
+  </si>
+  <si>
     <t xml:space="preserve">No</t>
   </si>
   <si>
-    <t xml:space="preserve">Matches the plan: 11 No. 8" side-entry shallow bases at LOC-01. The 3 No. cable-only fittings at LOC-01 keep their existing base and need none.</t>
+    <t xml:space="preserve">11 No. 8" side-entry shallow bases at LOC-01. 7 No. short of ADB SAFEGATE stock and drawn from ADA inventory, which holds 10 No. — 3 No. remain after withdrawal.</t>
   </si>
   <si>
     <t xml:space="preserve">Earth cable</t>
@@ -130,16 +148,19 @@
     <t xml:space="preserve">Pair</t>
   </si>
   <si>
-    <t xml:space="preserve">REVISED — 2 pair per fitting x 19 No. = 38 No. The 33 No. advised was against 16 No. fittings, before the 3 No. cable-only fittings at LOC-01 came into scope.</t>
+    <t xml:space="preserve">2 pair per fitting x 19 No. = 38 No.</t>
   </si>
   <si>
     <t xml:space="preserve">Secondary cable (2c x 4 sq.mm)</t>
   </si>
   <si>
+    <t xml:space="preserve">10020584</t>
+  </si>
+  <si>
     <t xml:space="preserve">mtr</t>
   </si>
   <si>
-    <t xml:space="preserve">1 No. 2-core 4 sq.mm cable to each fitting, SBC and TCC alike — 7 No. SBC and 12 No. TCC = 19 No. runs. Saw cut route length is approx. 420 m; 1500 m covers the full manhole-to-light runs (no joints) plus terminations and tails — confirm against the run-by-run lengths.</t>
+    <t xml:space="preserve">1 No. 2-core 4 sq.mm cable to each fitting, SBC and TCC alike — 7 No. SBC and 12 No. TCC = 19 No. runs. 350 m short of ADB SAFEGATE stock and drawn from ADA inventory, which holds 1 RoL @ 2000 m — 1650 m remain on the roll after withdrawal.</t>
   </si>
   <si>
     <t xml:space="preserve">Masking tape</t>
@@ -148,61 +169,103 @@
     <t xml:space="preserve">Box</t>
   </si>
   <si>
-    <t xml:space="preserve">As advised, for general protection. The signboard masking is by matt black vinyl sticker — see the separate line below.</t>
+    <t xml:space="preserve">As advised, for general protection. The signboard masking is by matt black vinyl sticker — see note 7; there is no material line for it in this table.</t>
   </si>
   <si>
     <t xml:space="preserve">Shallow base 12 inch</t>
   </si>
   <si>
-    <t xml:space="preserve">ADDED — the plan needs 13 No. new bases: 11 No. 8" plus 2 No. 12" (LOC-02 TCCECH-03/008 and LOC-03 TCCECH-03/003). Not in the list as issued.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vinyl sticker, matt black — signboard masking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADDED — masks the direction signboards leading to E4 and E6 under Phase 1, R4; removed in Phase 3 before the functionality check. Quantity depends on the number of sign faces and their area, which the deck does not carry — to be measured on site.</t>
+    <t xml:space="preserve">The plan needs 13 No. new bases: 11 No. 8" plus 2 No. 12" (LOC-02 TCCECH-03/008 and LOC-03 TCCECH-03/003).</t>
   </si>
   <si>
     <t xml:space="preserve">Dummy plate (8" / 12")</t>
   </si>
   <si>
-    <t xml:space="preserve">ADDED — 13 No. open bases plus the 3 No. LOC-01 fittings kept under a plate during milling (Phase 1, R3). Confirm whether the plates already installed are recovered for reuse, and whether the 3 No. at LOC-03 also need one.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lines to procure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count of lines with a shortfall against the required quantity.</t>
+    <t xml:space="preserve">13 No. open bases plus the 3 No. LOC-01 fittings kept under a plate during milling (Phase 1, R3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lines drawn from ADA inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every other line is covered by ADB SAFEGATE stock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADA INVENTORY — ITEMS TO BE WITHDRAWN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description as held in ADA inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Withdrawal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASE, MOUNTING; TYP: HIGH PRESSURE INJECTION SHALLOW, DIA 8IN; MFR: ADB SAFEGATE; P/N MSBC122V0003; M10; HS 85309000; with earthing connection, fixing screw set, one side cable entry (pole qty 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABLE, ELECTRICAL; CNDCTR DIA 4MM2; CNDCTR QTY 2C; MFR: EUPEN; 1 RoL / 2000 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RoL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350 m off the roll</t>
   </si>
   <si>
     <t xml:space="preserve">NOTES</t>
   </si>
   <si>
-    <t xml:space="preserve">1.  Rows 1–8 are the quantities as advised. Rows 9 to 11 are added, and the connector quantity is revised, so the list covers what the Rev P08 plan requires. Availability of the added lines is to be filled in (yellow cells).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.  The plan needs 13 No. new side-entry shallow bases in total — 11 No. 8" at LOC-01, 1 No. 12" at LOC-02 (TCCECH-03/008) and 1 No. 12" at LOC-03 (TCCECH-03/003).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.  Sealant, mortar and backer rod quantities depend on the saw cut width and depth and on the core diameter. Both are set by the saw cut &amp; side-entry shallow base detail drawing, which had not been issued at Rev P08 (hold point H5). Re-check these three lines when it is issued.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.  One 2-core 4 sq.mm secondary cable serves each fitting, SBC and TCC alike — 7 No. SBC and 12 No. TCC. Cable is ordered against the full manhole-to-light runs (19 No.), not the saw cut length — the cut measures approx. 420 m across the three locations (approx. 300 m LOC-01, 24 m LOC-02, 95 m LOC-03).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.  Saw cut is an interim arrangement agreed between the AGL team, the civil team and ADA AGL. Permanent duct provision follows under the South Rehabilitation works, and is not covered by this requirement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.  The direction signboards leading to E4 and E6 are masked with matt black vinyl sticker under Phase 1 (R4) and unmasked in Phase 3 before the functionality check. The vinyl quantity depends on the number of sign faces and their area — measure on site before ordering.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.  Testing and commissioning is carried out at circuit level and covers the affected fittings together with the fittings on the same circuits that fall outside these works — the series circuits are proved end to end before handover.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.  Remaining Qty is a formula (Required − Available). Edit only the Required and Available columns.</t>
+    <t xml:space="preserve">1.  Two lines fall short of ADB SAFEGATE stock — 7 No. shallow base 8 inch and 350 m of secondary cable. The project team confirms no ready stock; both are held in ADA inventory and are to be drawn from there under items 10016966 and 10020584.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.  ADA inventory balance after withdrawal: 3 No. shallow base 8 inch, and 1650 m remaining on the 2000 m cable roll. The roll is issued whole, so the balance stays on it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.  Confirm that ADA item 10016966 is the side-entry type the plan calls for. The stores description reads 'one side cable entry', which is consistent, but the part number should be checked against the base required before withdrawal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.  Confirm the rating of ADA item 10020584 against the ADA specification for the series secondary circuit. The stores description reads 2750.1 kV, which appears to be a data-entry artefact rather than the cable rating.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.  The plan needs 13 No. new side-entry shallow bases in total — 11 No. 8" at LOC-01, 1 No. 12" at LOC-02 (TCCECH-03/008) and 1 No. 12" at LOC-03 (TCCECH-03/003).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.  Sealant, mortar and backer rod quantities depend on the saw cut width and depth and on the core diameter. Both are set by the saw cut &amp; side-entry shallow base detail drawing, which had not been issued at Rev P08 (hold point H5). Re-check these three lines when it is issued.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.  The direction signboards leading to E4 and E6 are masked with matt black vinyl sticker under Phase 1 (R4) and unmasked in Phase 3 before the functionality check. There is no material line for the vinyl in this table — add one once the sign faces are measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.  One 2-core 4 sq.mm secondary cable serves each fitting, SBC and TCC alike — 7 No. SBC and 12 No. TCC. Cable is ordered against the full manhole-to-light runs (19 No.), not the saw cut length — the cut measures approx. 420 m across the three locations (approx. 300 m LOC-01, 24 m LOC-02, 95 m LOC-03).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.  Saw cut is an interim arrangement agreed between the AGL team, the civil team and ADA AGL. Permanent duct provision follows under the South Rehabilitation works, and is not covered by this requirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.  Testing and commissioning is carried out at circuit level and covers the affected fittings together with the fittings on the same circuits that fall outside these works — the series circuits are proved end to end before handover.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.  Qty requested from ADA inventory and the balance after withdrawal are formulas. Edit only Required Qty, Available with ADB SAFEGATE, and ADA inventory current stock.</t>
   </si>
 </sst>
 </file>
@@ -214,7 +277,7 @@
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,8 +361,15 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F2937"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -315,19 +385,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6F8"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE8F1F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF4D6"/>
+        <fgColor rgb="FFE8F1F5"/>
         <bgColor rgb="FFF4F6F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -380,7 +444,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -453,7 +517,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -461,10 +525,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -487,6 +547,18 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -522,8 +594,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF4D6"/>
       <rgbColor rgb="FFF4F6F8"/>
+      <rgbColor rgb="FFE8F1F5"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -745,16 +817,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -807,404 +880,625 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="5" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
+      <c r="F11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="7" t="s">
+      <c r="B12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <f aca="false">IF(E11="","",D11-E11)</f>
+      <c r="G12" s="10" t="n">
+        <f aca="false">MAX(0,E12-F12)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="n">
+      <c r="H12" s="9"/>
+      <c r="I12" s="10" t="str">
+        <f aca="false">IF(H12="","",H12-G12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="14" t="n">
+      <c r="B13" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="F13" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="F12" s="15" t="n">
-        <f aca="false">IF(E12="","",D12-E12)</f>
+      <c r="G13" s="15" t="n">
+        <f aca="false">MAX(0,E13-F13)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
+      <c r="H13" s="14"/>
+      <c r="I13" s="15" t="str">
+        <f aca="false">IF(H13="","",H13-G13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="9" t="n">
+      <c r="B14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="F14" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="10" t="n">
-        <f aca="false">IF(E13="","",D13-E13)</f>
+      <c r="G14" s="10" t="n">
+        <f aca="false">MAX(0,E14-F14)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="n">
+      <c r="H14" s="9"/>
+      <c r="I14" s="10" t="str">
+        <f aca="false">IF(H14="","",H14-G14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="14" t="n">
+      <c r="B15" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="F15" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="15" t="n">
-        <f aca="false">IF(E14="","",D14-E14)</f>
+      <c r="G15" s="20" t="n">
+        <f aca="false">MAX(0,E15-F15)</f>
         <v>7</v>
       </c>
-      <c r="G14" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
+      <c r="H15" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <f aca="false">IF(H15="","",H15-G15)</f>
+        <v>3</v>
+      </c>
+      <c r="J15" s="21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="9" t="n">
+      <c r="B16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="9" t="n">
         <v>900</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="F16" s="9" t="n">
         <v>900</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <f aca="false">IF(E15="","",D15-E15)</f>
+      <c r="G16" s="10" t="n">
+        <f aca="false">MAX(0,E16-F16)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="n">
+      <c r="H16" s="9"/>
+      <c r="I16" s="10" t="str">
+        <f aca="false">IF(H16="","",H16-G16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B17" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <f aca="false">MAX(0,E17-F17)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="14"/>
+      <c r="I17" s="15" t="str">
+        <f aca="false">IF(H17="","",H17-G17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>950</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="G18" s="20" t="n">
+        <f aca="false">MAX(0,E18-F18)</f>
+        <v>350</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I18" s="20" t="n">
+        <f aca="false">IF(H18="","",H18-G18)</f>
+        <v>1650</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <f aca="false">MAX(0,E19-F19)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="14"/>
+      <c r="I19" s="15" t="str">
+        <f aca="false">IF(H19="","",H19-G19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <f aca="false">MAX(0,E20-F20)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="9"/>
+      <c r="I20" s="10" t="str">
+        <f aca="false">IF(H20="","",H20-G20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <f aca="false">MAX(0,E21-F21)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="14"/>
+      <c r="I21" s="15" t="str">
+        <f aca="false">IF(H21="","",H21-G21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="22"/>
+      <c r="B22" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="24" t="n">
+        <f aca="false">COUNTIF(G12:G21,"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+    </row>
+    <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>38</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>33</v>
-      </c>
-      <c r="F16" s="15" t="n">
-        <f aca="false">IF(E16="","",D16-E16)</f>
-        <v>5</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>600</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <f aca="false">IF(E17="","",D17-E17)</f>
-        <v>900</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <f aca="false">IF(E18="","",D18-E18)</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="20"/>
-      <c r="F19" s="21" t="str">
-        <f aca="false">IF(E19="","",D19-E19)</f>
-        <v/>
-      </c>
-      <c r="G19" s="22" t="s">
+      <c r="C26" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+    </row>
+    <row r="27" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="27" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="21" t="str">
-        <f aca="false">IF(E20="","",D20-E20)</f>
-        <v/>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="E21" s="20"/>
-      <c r="F21" s="21" t="str">
-        <f aca="false">IF(E21="","",D21-E21)</f>
-        <v/>
-      </c>
-      <c r="G21" s="22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="23"/>
-      <c r="B22" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="25" t="n">
-        <f aca="false">COUNTIF(F11:F21,"&gt;0")</f>
-        <v>3</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-    </row>
-    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-    </row>
-    <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
+      <c r="C27" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="27" t="s">
+        <v>68</v>
+      </c>
       <c r="G27" s="27"/>
-    </row>
-    <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-    </row>
-    <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="25" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
+      <c r="A30" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
+      <c r="A31" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
     </row>
     <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
+      <c r="A32" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+    </row>
+    <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+    </row>
+    <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+    </row>
+    <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+    </row>
+    <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+    </row>
+    <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+    </row>
+    <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
+    </row>
+    <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+    </row>
+    <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
+  <mergeCells count="14">
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="F26:J26"/>
+    <mergeCell ref="F27:J27"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A40:J40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/skills/zia-mta-basemap/examples/twy-e-asbuilt-ducts/material/Material Requirement - TWY E AGL Installation - Rev P08.xlsx
+++ b/skills/zia-mta-basemap/examples/twy-e-asbuilt-ducts/material/Material Requirement - TWY E AGL Installation - Rev P08.xlsx
@@ -160,7 +160,7 @@
     <t xml:space="preserve">mtr</t>
   </si>
   <si>
-    <t xml:space="preserve">1 No. 2-core 4 sq.mm cable to each fitting, SBC and TCC alike — 7 No. SBC and 12 No. TCC = 19 No. runs. 350 m short of ADB SAFEGATE stock and drawn from ADA inventory, which holds 1 RoL @ 2000 m — 1650 m remain on the roll after withdrawal.</t>
+    <t xml:space="preserve">1 No. 2-core 4 sq.mm cable to each fitting, SBC and TCC alike — 19 No. runs totalling 950 m: LOC-01 700 m over 14 No., LOC-02 50 m over 1 No., LOC-03 200 m over 4 No. 350 m short of ADB SAFEGATE stock and drawn from ADA inventory, which holds 1 RoL @ 2000 m — 1650 m remain on the roll after withdrawal.</t>
   </si>
   <si>
     <t xml:space="preserve">Masking tape</t>
@@ -256,7 +256,7 @@
     <t xml:space="preserve">7.  The direction signboards leading to E4 and E6 are masked with matt black vinyl sticker under Phase 1 (R4) and unmasked in Phase 3 before the functionality check. There is no material line for the vinyl in this table — add one once the sign faces are measured.</t>
   </si>
   <si>
-    <t xml:space="preserve">8.  One 2-core 4 sq.mm secondary cable serves each fitting, SBC and TCC alike — 7 No. SBC and 12 No. TCC. Cable is ordered against the full manhole-to-light runs (19 No.), not the saw cut length — the cut measures approx. 420 m across the three locations (approx. 300 m LOC-01, 24 m LOC-02, 95 m LOC-03).</t>
+    <t xml:space="preserve">8.  One 2-core 4 sq.mm secondary cable serves each fitting, SBC and TCC alike — 7 No. SBC and 12 No. TCC. The 950 m is the ordered length for the full manhole-to-light runs at an average 50 m per run — LOC-01 700 m, LOC-02 50 m, LOC-03 200 m. It is not the saw cut length, which measures approx. 420 m (approx. 300 m LOC-01, 24 m LOC-02, 95 m LOC-03).</t>
   </si>
   <si>
     <t xml:space="preserve">9.  Saw cut is an interim arrangement agreed between the AGL team, the civil team and ADA AGL. Permanent duct provision follows under the South Rehabilitation works, and is not covered by this requirement.</t>
